--- a/Config/Excels/__enums__.xlsx
+++ b/Config/Excels/__enums__.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145">
   <si>
     <t>##var</t>
   </si>
@@ -413,6 +413,42 @@
   </si>
   <si>
     <t>特效</t>
+  </si>
+  <si>
+    <t>引导步骤类型</t>
+  </si>
+  <si>
+    <t>EStepType</t>
+  </si>
+  <si>
+    <t>无类型</t>
+  </si>
+  <si>
+    <t>ClickUI</t>
+  </si>
+  <si>
+    <t>点击UI</t>
+  </si>
+  <si>
+    <t>点击UI引导</t>
+  </si>
+  <si>
+    <t>Dialog</t>
+  </si>
+  <si>
+    <t>对话</t>
+  </si>
+  <si>
+    <t>对话引导</t>
+  </si>
+  <si>
+    <t>Wait</t>
+  </si>
+  <si>
+    <t>等待</t>
+  </si>
+  <si>
+    <t>等待步骤</t>
   </si>
 </sst>
 </file>
@@ -420,10 +456,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -449,7 +485,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -457,7 +493,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -473,35 +517,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -539,7 +554,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -547,7 +562,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -569,9 +606,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -585,7 +621,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -630,13 +666,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -648,163 +810,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -859,9 +901,44 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -877,15 +954,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -908,8 +976,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -928,32 +996,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -962,10 +1004,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="9">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
@@ -974,19 +1016,19 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
@@ -995,116 +1037,116 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1134,6 +1176,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1191,11 +1236,6 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="00EE7228"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1462,7 +1502,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK56"/>
+  <dimension ref="A1:AK60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.125" style="4" customWidth="1"/>
@@ -1503,10 +1543,10 @@
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="13"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:12">
       <c r="A2" s="5" t="s">
@@ -3266,6 +3306,99 @@
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
+    <row r="57" spans="1:12">
+      <c r="A57" t="s">
+        <v>133</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C57" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D57" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J57" s="11">
+        <v>0</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L57" s="11"/>
+    </row>
+    <row r="58" spans="2:12">
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J58" s="11">
+        <v>1</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="L58" s="11"/>
+    </row>
+    <row r="59" spans="2:12">
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="J59" s="11">
+        <v>2</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="L59" s="11"/>
+    </row>
+    <row r="60" spans="2:12">
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="J60" s="11">
+        <v>3</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="L60" s="11"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Config/Excels/__enums__.xlsx
+++ b/Config/Excels/__enums__.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169">
   <si>
     <t>##var</t>
   </si>
@@ -449,6 +449,78 @@
   </si>
   <si>
     <t>等待步骤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUILayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorldUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">世界场景UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一般全屏界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">窗口</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">提示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">引导</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加载界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">界面层级</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUITweenType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无动画</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">淡入淡出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自定义动画</t>
+  </si>
+  <si>
+    <t xml:space="preserve">动画类型</t>
   </si>
 </sst>
 </file>
@@ -1500,9 +1572,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:AK60"/>
+  <dimension ref="A1:AK72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.125" style="4" customWidth="1"/>
@@ -3399,6 +3471,198 @@
       </c>
       <c r="L60" s="11"/>
     </row>
+    <row r="61" s="2" customFormat="1" spans="1:12">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" t="b">
+        <v>0</v>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>146</v>
+      </c>
+      <c r="I62" t="s">
+        <v>147</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="H63" t="s">
+        <v>148</v>
+      </c>
+      <c r="I63" t="s">
+        <v>149</v>
+      </c>
+      <c r="J63">
+        <v>1500</v>
+      </c>
+      <c r="K63" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="H64" t="s">
+        <v>150</v>
+      </c>
+      <c r="I64" t="s">
+        <v>151</v>
+      </c>
+      <c r="J64">
+        <v>2000</v>
+      </c>
+      <c r="K64" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="H65" t="s">
+        <v>152</v>
+      </c>
+      <c r="I65" t="s">
+        <v>153</v>
+      </c>
+      <c r="J65">
+        <v>2500</v>
+      </c>
+      <c r="K65" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="H66" t="s">
+        <v>154</v>
+      </c>
+      <c r="I66" t="s">
+        <v>155</v>
+      </c>
+      <c r="J66">
+        <v>3000</v>
+      </c>
+      <c r="K66" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="H67" t="s">
+        <v>156</v>
+      </c>
+      <c r="I67" t="s">
+        <v>157</v>
+      </c>
+      <c r="J67">
+        <v>3500</v>
+      </c>
+      <c r="K67" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="H68" t="s">
+        <v>158</v>
+      </c>
+      <c r="I68" t="s">
+        <v>159</v>
+      </c>
+      <c r="J68">
+        <v>4000</v>
+      </c>
+      <c r="K68" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" spans="1:12">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" t="s">
+        <v>161</v>
+      </c>
+      <c r="C70" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>162</v>
+      </c>
+      <c r="I70" t="s">
+        <v>163</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="H71" t="s">
+        <v>164</v>
+      </c>
+      <c r="I71" t="s">
+        <v>165</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="H72" t="s">
+        <v>166</v>
+      </c>
+      <c r="I72" t="s">
+        <v>167</v>
+      </c>
+      <c r="J72">
+        <v>2</v>
+      </c>
+      <c r="K72" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Config/Excels/__enums__.xlsx
+++ b/Config/Excels/__enums__.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168">
   <si>
     <t>##var</t>
   </si>
@@ -451,76 +451,73 @@
     <t>等待步骤</t>
   </si>
   <si>
-    <t xml:space="preserve">EUILayer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WorldUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">世界场景UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">主界面</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一般全屏界面</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">窗口</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">提示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">引导</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">加载界面</t>
-  </si>
-  <si>
-    <t xml:space="preserve">界面层级</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUITweenType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">无动画</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">淡入淡出</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自定义动画</t>
-  </si>
-  <si>
-    <t xml:space="preserve">动画类型</t>
+    <t>UI界面层级</t>
+  </si>
+  <si>
+    <t>EUILayer</t>
+  </si>
+  <si>
+    <t>WorldUI</t>
+  </si>
+  <si>
+    <t>世界场景UI</t>
+  </si>
+  <si>
+    <t>MainUI</t>
+  </si>
+  <si>
+    <t>主界面</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>一般全屏界面</t>
+  </si>
+  <si>
+    <t>Window</t>
+  </si>
+  <si>
+    <t>窗口</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>提示</t>
+  </si>
+  <si>
+    <t>Guide</t>
+  </si>
+  <si>
+    <t>引导</t>
+  </si>
+  <si>
+    <t>Loading</t>
+  </si>
+  <si>
+    <t>加载界面</t>
+  </si>
+  <si>
+    <t>UI界面动画类型</t>
+  </si>
+  <si>
+    <t>EUITweenType</t>
+  </si>
+  <si>
+    <t>无动画</t>
+  </si>
+  <si>
+    <t>Fade</t>
+  </si>
+  <si>
+    <t>淡入淡出</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>自定义动画</t>
   </si>
 </sst>
 </file>
@@ -528,8 +525,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
@@ -550,14 +547,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -573,7 +570,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -591,6 +588,28 @@
       <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -626,25 +645,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -655,8 +658,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -678,13 +682,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -693,7 +690,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -744,7 +741,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,13 +849,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -774,151 +921,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -982,39 +985,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1026,6 +996,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1048,8 +1027,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1068,6 +1047,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1076,10 +1079,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="11">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
@@ -1088,137 +1091,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="9">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1251,6 +1254,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1572,7 +1578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AK72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -1615,10 +1621,10 @@
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="14"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:12">
       <c r="A2" s="5" t="s">
@@ -3471,197 +3477,243 @@
       </c>
       <c r="L60" s="11"/>
     </row>
-    <row r="61" s="2" customFormat="1" spans="1:12">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
-    </row>
+    <row r="61" s="2" customFormat="1"/>
     <row r="62" spans="1:12">
-      <c r="A62" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="A62" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C62" t="b">
+      <c r="B62" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D62" t="b">
+      <c r="D62" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="H62" t="s">
-        <v>146</v>
-      </c>
-      <c r="I62" t="s">
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="J62">
+      <c r="I62" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="J62" s="12">
         <v>0</v>
       </c>
-      <c r="K62" t="s">
-        <v>147</v>
-      </c>
+      <c r="K62" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="L62" s="12"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="H63" t="s">
-        <v>148</v>
-      </c>
-      <c r="I63" t="s">
+      <c r="A63" s="2"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J63">
+      <c r="I63" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="J63" s="12">
         <v>1500</v>
       </c>
-      <c r="K63" t="s">
-        <v>149</v>
-      </c>
+      <c r="K63" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="L63" s="12"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="H64" t="s">
-        <v>150</v>
-      </c>
-      <c r="I64" t="s">
+      <c r="A64" s="2"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="J64">
+      <c r="I64" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J64" s="12">
         <v>2000</v>
       </c>
-      <c r="K64" t="s">
-        <v>151</v>
-      </c>
+      <c r="K64" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="L64" s="12"/>
     </row>
     <row r="65" spans="1:12">
-      <c r="H65" t="s">
-        <v>152</v>
-      </c>
-      <c r="I65" t="s">
+      <c r="A65" s="2"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="J65">
+      <c r="I65" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="J65" s="12">
         <v>2500</v>
       </c>
-      <c r="K65" t="s">
-        <v>153</v>
-      </c>
+      <c r="K65" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="L65" s="12"/>
     </row>
     <row r="66" spans="1:12">
-      <c r="H66" t="s">
-        <v>154</v>
-      </c>
-      <c r="I66" t="s">
+      <c r="A66" s="2"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="J66">
+      <c r="I66" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="J66" s="12">
         <v>3000</v>
       </c>
-      <c r="K66" t="s">
-        <v>155</v>
-      </c>
+      <c r="K66" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="L66" s="12"/>
     </row>
     <row r="67" spans="1:12">
-      <c r="H67" t="s">
-        <v>156</v>
-      </c>
-      <c r="I67" t="s">
+      <c r="A67" s="2"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="J67">
+      <c r="I67" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J67" s="12">
         <v>3500</v>
       </c>
-      <c r="K67" t="s">
-        <v>157</v>
-      </c>
+      <c r="K67" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="L67" s="12"/>
     </row>
     <row r="68" spans="1:12">
-      <c r="H68" t="s">
-        <v>158</v>
-      </c>
-      <c r="I68" t="s">
+      <c r="A68" s="2"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="J68">
+      <c r="I68" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="J68" s="12">
         <v>4000</v>
       </c>
-      <c r="K68" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:12">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
-    </row>
+      <c r="K68" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="L68" s="12"/>
+    </row>
+    <row r="69" s="2" customFormat="1"/>
     <row r="70" spans="1:12">
-      <c r="A70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="A70" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C70" t="b">
+      <c r="B70" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C70" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D70" t="b">
+      <c r="D70" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="H70" t="s">
-        <v>162</v>
-      </c>
-      <c r="I70" t="s">
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I70" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="J70">
+      <c r="J70" s="12">
         <v>0</v>
       </c>
-      <c r="K70" t="s">
+      <c r="K70" s="12" t="s">
         <v>163</v>
       </c>
+      <c r="L70" s="12"/>
     </row>
     <row r="71" spans="1:12">
-      <c r="H71" t="s">
+      <c r="A71" s="2"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I71" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="J71">
+      <c r="J71" s="12">
         <v>1</v>
       </c>
-      <c r="K71" t="s">
+      <c r="K71" s="12" t="s">
         <v>165</v>
       </c>
+      <c r="L71" s="12"/>
     </row>
     <row r="72" spans="1:12">
-      <c r="H72" t="s">
+      <c r="A72" s="2"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I72" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="J72">
+      <c r="J72" s="12">
         <v>2</v>
       </c>
-      <c r="K72" t="s">
+      <c r="K72" s="12" t="s">
         <v>167</v>
       </c>
+      <c r="L72" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Config/Excels/__enums__.xlsx
+++ b/Config/Excels/__enums__.xlsx
@@ -14,11 +14,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176">
   <si>
     <t>##var</t>
   </si>
   <si>
+    <t>##注释</t>
+  </si>
+  <si>
     <t>full_name</t>
   </si>
   <si>
@@ -338,6 +341,27 @@
   </si>
   <si>
     <t>界面关闭时框架自动清除</t>
+  </si>
+  <si>
+    <t>红点计算逻辑类型</t>
+  </si>
+  <si>
+    <t>ERedDotLogicType</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>求和</t>
+  </si>
+  <si>
+    <t>求和(业务代码显式调用)</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>任意一个即可</t>
   </si>
   <si>
     <t>声音组</t>
@@ -525,8 +549,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
@@ -547,13 +571,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -562,7 +579,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -571,6 +588,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -586,35 +610,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -645,14 +640,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -661,6 +656,21 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -682,9 +692,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -747,7 +771,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,67 +831,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -831,37 +855,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -873,13 +867,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -897,13 +885,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -915,13 +939,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -974,13 +998,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1009,6 +1037,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1027,47 +1079,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1079,10 +1103,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="9">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
@@ -1091,137 +1115,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7">
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="39" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1232,35 +1256,41 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="31" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="31" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1580,223 +1610,228 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK72"/>
+  <dimension ref="A1:AL75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="22.375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="7.125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="9.375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="13" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="12.125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="26.625" style="4" customWidth="1"/>
+    <col min="1" max="2" width="17.125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22.375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="14.125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="7.125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9.375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="5" style="5" customWidth="1"/>
+    <col min="9" max="9" width="13" style="5" customWidth="1"/>
+    <col min="10" max="10" width="16.5" style="5" customWidth="1"/>
+    <col min="11" max="11" width="12.125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="26.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="29" customHeight="1" spans="1:12">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="1" customFormat="1" ht="29" customHeight="1" spans="1:13">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
       <c r="L1" s="14"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:12">
-      <c r="A2" s="5" t="s">
+      <c r="M1" s="15"/>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:13">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="K2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:12">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="M2" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:13">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="5"/>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:12">
-      <c r="A4" s="2" t="s">
+      <c r="L3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="2:13">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="7" t="b">
+      <c r="C4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="D4" s="7" t="b">
+      <c r="E4" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="H4" s="7"/>
       <c r="I4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="7">
         <v>1</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="2:12">
-      <c r="B5" s="7"/>
+      <c r="L4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="7"/>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="3:13">
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="7">
         <v>2</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="7"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="2:12">
-      <c r="B6" s="7"/>
+      <c r="L5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="7"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="3:13">
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="7">
         <v>3</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="7"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="2:12">
-      <c r="B7" s="7"/>
+      <c r="L6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="7"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="3:13">
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="H7" s="7"/>
       <c r="I7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="7">
         <v>4</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="7"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="2:12">
-      <c r="B8" s="7"/>
+      <c r="L7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="7"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="3:13">
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="H8" s="7"/>
       <c r="I8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="7">
         <v>5</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="7"/>
-    </row>
-    <row r="9" spans="1:37">
+      <c r="L8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" s="7"/>
+    </row>
+    <row r="9" spans="1:38">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1834,122 +1869,123 @@
       <c r="AI9" s="2"/>
       <c r="AJ9" s="2"/>
       <c r="AK9" s="2"/>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:12">
-      <c r="A10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="AL9" s="2"/>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="2:13">
+      <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="8" t="b">
+      <c r="C10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D10" s="8" t="b">
+      <c r="E10" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="8" t="s">
-        <v>33</v>
-      </c>
+      <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="8">
         <v>1</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="8"/>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="2:12">
-      <c r="B11" s="8"/>
+      <c r="L10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="3:13">
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="H11" s="8"/>
       <c r="I11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="8">
         <v>2</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11" s="8"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="2:12">
-      <c r="B12" s="8"/>
+      <c r="L11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="8"/>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="3:13">
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="8" t="s">
-        <v>37</v>
-      </c>
+      <c r="H12" s="8"/>
       <c r="I12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="8">
         <v>3</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L12" s="8"/>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="2:12">
-      <c r="B13" s="8"/>
+      <c r="L12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12" s="8"/>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="3:13">
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="8">
         <v>4</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L13" s="8"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="2:12">
-      <c r="B14" s="8"/>
+      <c r="L13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M13" s="8"/>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="3:13">
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="8" t="s">
-        <v>41</v>
-      </c>
+      <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="8">
         <v>5</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="L14" s="8"/>
-    </row>
-    <row r="15" spans="1:37">
+      <c r="L14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" s="8"/>
+    </row>
+    <row r="15" spans="1:38">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1987,143 +2023,144 @@
       <c r="AI15" s="2"/>
       <c r="AJ15" s="2"/>
       <c r="AK15" s="2"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:12">
-      <c r="A16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="AL15" s="2"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="2:13">
+      <c r="B16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="8" t="b">
+      <c r="C16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D16" s="8" t="b">
+      <c r="E16" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-      <c r="H16" s="8" t="s">
-        <v>45</v>
-      </c>
+      <c r="H16" s="8"/>
       <c r="I16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K16" s="8">
         <v>0</v>
       </c>
-      <c r="K16" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" s="8"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="2:12">
-      <c r="B17" s="8"/>
+      <c r="L16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M16" s="8"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="3:13">
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="8" t="s">
-        <v>47</v>
-      </c>
+      <c r="H17" s="8"/>
       <c r="I17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="8">
         <v>1</v>
       </c>
-      <c r="K17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="L17" s="8"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="2:12">
-      <c r="B18" s="8"/>
+      <c r="L17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="8"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="3:13">
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="8" t="s">
-        <v>49</v>
-      </c>
+      <c r="H18" s="8"/>
       <c r="I18" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="8">
         <v>2</v>
       </c>
-      <c r="K18" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="L18" s="8"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="2:12">
-      <c r="B19" s="8"/>
+      <c r="L18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M18" s="8"/>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="3:13">
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="8" t="s">
-        <v>51</v>
-      </c>
+      <c r="H19" s="8"/>
       <c r="I19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" s="8">
         <v>3</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="L19" s="8"/>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="2:12">
-      <c r="B20" s="8"/>
+      <c r="L19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M19" s="8"/>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="3:13">
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="8" t="s">
-        <v>53</v>
-      </c>
+      <c r="H20" s="8"/>
       <c r="I20" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K20" s="8">
         <v>4</v>
       </c>
-      <c r="K20" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L20" s="8"/>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="2:12">
-      <c r="B21" s="8"/>
+      <c r="L20" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20" s="8"/>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="3:13">
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="8" t="s">
-        <v>55</v>
-      </c>
+      <c r="H21" s="8"/>
       <c r="I21" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21" s="8">
         <v>5</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="1:37">
+      <c r="L21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="8"/>
+    </row>
+    <row r="22" spans="1:38">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2161,80 +2198,81 @@
       <c r="AI22" s="2"/>
       <c r="AJ22" s="2"/>
       <c r="AK22" s="2"/>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:12">
-      <c r="A23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="8" t="s">
+      <c r="AL22" s="2"/>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="2:13">
+      <c r="B23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="8" t="b">
+      <c r="C23" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="D23" s="8" t="b">
+      <c r="E23" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
-      <c r="H23" s="8" t="s">
-        <v>59</v>
-      </c>
+      <c r="H23" s="8"/>
       <c r="I23" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K23" s="8">
         <v>0</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="L23" s="8"/>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="2:12">
-      <c r="B24" s="8"/>
+      <c r="L23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="8"/>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="3:13">
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
-      <c r="H24" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="H24" s="8"/>
       <c r="I24" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K24" s="8">
         <v>1</v>
       </c>
-      <c r="K24" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="L24" s="8"/>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="2:12">
-      <c r="B25" s="8"/>
+      <c r="L24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M24" s="8"/>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="3:13">
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
-      <c r="H25" s="8" t="s">
-        <v>63</v>
-      </c>
+      <c r="H25" s="8"/>
       <c r="I25" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K25" s="8">
         <v>2</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="L25" s="8"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:37">
+      <c r="L25" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M25" s="8"/>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="1:38">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2272,37 +2310,38 @@
       <c r="AI26" s="2"/>
       <c r="AJ26" s="2"/>
       <c r="AK26" s="2"/>
-    </row>
-    <row r="27" spans="1:37">
-      <c r="A27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="9" t="s">
+      <c r="AL26" s="2"/>
+    </row>
+    <row r="27" spans="1:38">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="9" t="b">
+      <c r="C27" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="D27" s="9" t="b">
+      <c r="E27" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="H27" s="9" t="s">
-        <v>68</v>
-      </c>
+      <c r="H27" s="9"/>
       <c r="I27" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K27" s="9">
         <v>1000</v>
       </c>
-      <c r="K27" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="L27" s="9"/>
-      <c r="M27" s="2"/>
+      <c r="L27" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="M27" s="9"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -2327,29 +2366,30 @@
       <c r="AI27" s="2"/>
       <c r="AJ27" s="2"/>
       <c r="AK27" s="2"/>
-    </row>
-    <row r="28" spans="1:37">
+      <c r="AL27" s="2"/>
+    </row>
+    <row r="28" spans="1:38">
       <c r="A28" s="2"/>
-      <c r="B28" s="9"/>
+      <c r="B28" s="2"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="9" t="s">
-        <v>70</v>
-      </c>
+      <c r="H28" s="9"/>
       <c r="I28" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="K28" s="9">
         <v>1001</v>
       </c>
-      <c r="K28" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="L28" s="9"/>
-      <c r="M28" s="2"/>
+      <c r="L28" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="M28" s="9"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -2374,29 +2414,30 @@
       <c r="AI28" s="2"/>
       <c r="AJ28" s="2"/>
       <c r="AK28" s="2"/>
-    </row>
-    <row r="29" spans="1:37">
+      <c r="AL28" s="2"/>
+    </row>
+    <row r="29" spans="1:38">
       <c r="A29" s="2"/>
-      <c r="B29" s="9"/>
+      <c r="B29" s="2"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="9" t="s">
-        <v>72</v>
-      </c>
+      <c r="H29" s="9"/>
       <c r="I29" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="K29" s="9">
         <v>1002</v>
       </c>
-      <c r="K29" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="L29" s="9"/>
-      <c r="M29" s="2"/>
+      <c r="L29" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="M29" s="9"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -2421,29 +2462,30 @@
       <c r="AI29" s="2"/>
       <c r="AJ29" s="2"/>
       <c r="AK29" s="2"/>
-    </row>
-    <row r="30" spans="1:37">
+      <c r="AL29" s="2"/>
+    </row>
+    <row r="30" spans="1:38">
       <c r="A30" s="2"/>
-      <c r="B30" s="9"/>
+      <c r="B30" s="2"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
-      <c r="H30" s="9" t="s">
-        <v>74</v>
-      </c>
+      <c r="H30" s="9"/>
       <c r="I30" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="K30" s="9">
         <v>2000</v>
       </c>
-      <c r="K30" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="L30" s="9"/>
-      <c r="M30" s="2"/>
+      <c r="L30" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M30" s="9"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -2468,29 +2510,30 @@
       <c r="AI30" s="2"/>
       <c r="AJ30" s="2"/>
       <c r="AK30" s="2"/>
-    </row>
-    <row r="31" spans="1:37">
+      <c r="AL30" s="2"/>
+    </row>
+    <row r="31" spans="1:38">
       <c r="A31" s="2"/>
-      <c r="B31" s="9"/>
+      <c r="B31" s="2"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="9" t="s">
-        <v>76</v>
-      </c>
+      <c r="H31" s="9"/>
       <c r="I31" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K31" s="9">
         <v>2001</v>
       </c>
-      <c r="K31" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="L31" s="9"/>
-      <c r="M31" s="2"/>
+      <c r="L31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="M31" s="9"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -2515,29 +2558,30 @@
       <c r="AI31" s="2"/>
       <c r="AJ31" s="2"/>
       <c r="AK31" s="2"/>
-    </row>
-    <row r="32" spans="1:37">
+      <c r="AL31" s="2"/>
+    </row>
+    <row r="32" spans="1:38">
       <c r="A32" s="2"/>
-      <c r="B32" s="9"/>
+      <c r="B32" s="2"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
-      <c r="H32" s="9" t="s">
-        <v>78</v>
-      </c>
+      <c r="H32" s="9"/>
       <c r="I32" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K32" s="9">
         <v>2002</v>
       </c>
-      <c r="K32" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="L32" s="9"/>
-      <c r="M32" s="2"/>
+      <c r="L32" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M32" s="9"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -2562,29 +2606,30 @@
       <c r="AI32" s="2"/>
       <c r="AJ32" s="2"/>
       <c r="AK32" s="2"/>
-    </row>
-    <row r="33" spans="1:37">
+      <c r="AL32" s="2"/>
+    </row>
+    <row r="33" spans="1:38">
       <c r="A33" s="2"/>
-      <c r="B33" s="9"/>
+      <c r="B33" s="2"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
-      <c r="H33" s="9" t="s">
-        <v>80</v>
-      </c>
+      <c r="H33" s="9"/>
       <c r="I33" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="K33" s="9">
         <v>3000</v>
       </c>
-      <c r="K33" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="L33" s="9"/>
-      <c r="M33" s="2"/>
+      <c r="L33" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="M33" s="9"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -2609,29 +2654,30 @@
       <c r="AI33" s="2"/>
       <c r="AJ33" s="2"/>
       <c r="AK33" s="2"/>
-    </row>
-    <row r="34" spans="1:37">
+      <c r="AL33" s="2"/>
+    </row>
+    <row r="34" spans="1:38">
       <c r="A34" s="2"/>
-      <c r="B34" s="9"/>
+      <c r="B34" s="2"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="9" t="s">
-        <v>82</v>
-      </c>
+      <c r="H34" s="9"/>
       <c r="I34" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K34" s="9">
         <v>3001</v>
       </c>
-      <c r="K34" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="L34" s="9"/>
-      <c r="M34" s="2"/>
+      <c r="L34" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="M34" s="9"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -2656,29 +2702,30 @@
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
       <c r="AK34" s="2"/>
-    </row>
-    <row r="35" spans="1:37">
+      <c r="AL34" s="2"/>
+    </row>
+    <row r="35" spans="1:38">
       <c r="A35" s="2"/>
-      <c r="B35" s="9"/>
+      <c r="B35" s="2"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="9" t="s">
-        <v>84</v>
-      </c>
+      <c r="H35" s="9"/>
       <c r="I35" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="K35" s="9">
         <v>3002</v>
       </c>
-      <c r="K35" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="L35" s="9"/>
-      <c r="M35" s="2"/>
+      <c r="L35" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="M35" s="9"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -2703,29 +2750,30 @@
       <c r="AI35" s="2"/>
       <c r="AJ35" s="2"/>
       <c r="AK35" s="2"/>
-    </row>
-    <row r="36" spans="1:37">
+      <c r="AL35" s="2"/>
+    </row>
+    <row r="36" spans="1:38">
       <c r="A36" s="2"/>
-      <c r="B36" s="9"/>
+      <c r="B36" s="2"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
-      <c r="H36" s="9" t="s">
-        <v>86</v>
-      </c>
+      <c r="H36" s="9"/>
       <c r="I36" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K36" s="9">
         <v>3003</v>
       </c>
-      <c r="K36" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="L36" s="9"/>
-      <c r="M36" s="2"/>
+      <c r="L36" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M36" s="9"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -2750,29 +2798,30 @@
       <c r="AI36" s="2"/>
       <c r="AJ36" s="2"/>
       <c r="AK36" s="2"/>
-    </row>
-    <row r="37" spans="1:37">
+      <c r="AL36" s="2"/>
+    </row>
+    <row r="37" spans="1:38">
       <c r="A37" s="2"/>
-      <c r="B37" s="9"/>
+      <c r="B37" s="2"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
-      <c r="H37" s="9" t="s">
-        <v>88</v>
-      </c>
+      <c r="H37" s="9"/>
       <c r="I37" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="K37" s="9">
         <v>4000</v>
       </c>
-      <c r="K37" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="L37" s="9"/>
-      <c r="M37" s="2"/>
+      <c r="L37" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M37" s="9"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -2797,29 +2846,30 @@
       <c r="AI37" s="2"/>
       <c r="AJ37" s="2"/>
       <c r="AK37" s="2"/>
-    </row>
-    <row r="38" spans="1:37">
+      <c r="AL37" s="2"/>
+    </row>
+    <row r="38" spans="1:38">
       <c r="A38" s="2"/>
-      <c r="B38" s="9"/>
+      <c r="B38" s="2"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
-      <c r="H38" s="9" t="s">
-        <v>90</v>
-      </c>
+      <c r="H38" s="9"/>
       <c r="I38" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="K38" s="9">
         <v>4001</v>
       </c>
-      <c r="K38" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="L38" s="9"/>
-      <c r="M38" s="2"/>
+      <c r="L38" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="M38" s="9"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -2844,8 +2894,9 @@
       <c r="AI38" s="2"/>
       <c r="AJ38" s="2"/>
       <c r="AK38" s="2"/>
-    </row>
-    <row r="39" spans="1:37">
+      <c r="AL38" s="2"/>
+    </row>
+    <row r="39" spans="1:38">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2883,37 +2934,38 @@
       <c r="AI39" s="2"/>
       <c r="AJ39" s="2"/>
       <c r="AK39" s="2"/>
-    </row>
-    <row r="40" spans="1:37">
-      <c r="A40" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B40" s="9" t="s">
+      <c r="AL39" s="2"/>
+    </row>
+    <row r="40" spans="1:38">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="9" t="b">
+      <c r="C40" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="D40" s="9" t="b">
+      <c r="E40" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
-      <c r="H40" s="9" t="s">
-        <v>94</v>
-      </c>
+      <c r="H40" s="9"/>
       <c r="I40" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="J40" s="9">
+      <c r="J40" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="K40" s="9">
         <v>0</v>
       </c>
-      <c r="K40" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="L40" s="9"/>
-      <c r="M40" s="2"/>
+      <c r="L40" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="M40" s="9"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -2938,29 +2990,30 @@
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
       <c r="AK40" s="2"/>
-    </row>
-    <row r="41" spans="1:37">
+      <c r="AL40" s="2"/>
+    </row>
+    <row r="41" spans="1:38">
       <c r="A41" s="2"/>
-      <c r="B41" s="9"/>
+      <c r="B41" s="2"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
-      <c r="H41" s="9" t="s">
-        <v>96</v>
-      </c>
+      <c r="H41" s="9"/>
       <c r="I41" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="J41" s="9">
+      <c r="J41" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K41" s="9">
         <v>1</v>
       </c>
-      <c r="K41" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="L41" s="9"/>
-      <c r="M41" s="2"/>
+      <c r="L41" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="M41" s="9"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
@@ -2985,27 +3038,28 @@
       <c r="AI41" s="2"/>
       <c r="AJ41" s="2"/>
       <c r="AK41" s="2"/>
-    </row>
-    <row r="42" spans="1:37">
+      <c r="AL41" s="2"/>
+    </row>
+    <row r="42" spans="1:38">
       <c r="A42" s="2"/>
-      <c r="B42" s="9"/>
+      <c r="B42" s="2"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="9"/>
-      <c r="H42" s="9" t="s">
-        <v>98</v>
-      </c>
+      <c r="H42" s="9"/>
       <c r="I42" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="J42" s="9">
+      <c r="J42" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="K42" s="9">
         <v>2</v>
       </c>
-      <c r="K42" s="9"/>
       <c r="L42" s="9"/>
-      <c r="M42" s="2"/>
+      <c r="M42" s="9"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -3030,8 +3084,9 @@
       <c r="AI42" s="2"/>
       <c r="AJ42" s="2"/>
       <c r="AK42" s="2"/>
-    </row>
-    <row r="43" spans="1:37">
+      <c r="AL42" s="2"/>
+    </row>
+    <row r="43" spans="1:38">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3069,37 +3124,38 @@
       <c r="AI43" s="2"/>
       <c r="AJ43" s="2"/>
       <c r="AK43" s="2"/>
-    </row>
-    <row r="44" spans="1:37">
-      <c r="A44" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B44" s="9" t="s">
+      <c r="AL43" s="2"/>
+    </row>
+    <row r="44" spans="1:38">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="9" t="b">
+      <c r="C44" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="D44" s="9" t="b">
+      <c r="E44" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
-      <c r="H44" s="9" t="s">
-        <v>102</v>
-      </c>
+      <c r="H44" s="9"/>
       <c r="I44" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="J44" s="9">
+      <c r="J44" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="K44" s="9">
         <v>0</v>
       </c>
-      <c r="K44" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="L44" s="9"/>
-      <c r="M44" s="2"/>
+      <c r="L44" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="M44" s="9"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
@@ -3124,29 +3180,30 @@
       <c r="AI44" s="2"/>
       <c r="AJ44" s="2"/>
       <c r="AK44" s="2"/>
-    </row>
-    <row r="45" spans="1:37">
+      <c r="AL44" s="2"/>
+    </row>
+    <row r="45" spans="1:38">
       <c r="A45" s="2"/>
-      <c r="B45" s="9"/>
+      <c r="B45" s="2"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
-      <c r="H45" s="9" t="s">
-        <v>105</v>
-      </c>
+      <c r="H45" s="9"/>
       <c r="I45" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K45" s="9">
         <v>1</v>
       </c>
-      <c r="K45" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="L45" s="9"/>
-      <c r="M45" s="2"/>
+      <c r="L45" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="M45" s="9"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
@@ -3171,553 +3228,711 @@
       <c r="AI45" s="2"/>
       <c r="AJ45" s="2"/>
       <c r="AK45" s="2"/>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="10" t="s">
+      <c r="AL45" s="2"/>
+    </row>
+    <row r="46" s="4" customFormat="1" spans="1:38">
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
+      <c r="U46" s="10"/>
+      <c r="V46" s="10"/>
+      <c r="W46" s="10"/>
+      <c r="X46" s="10"/>
+      <c r="Y46" s="10"/>
+      <c r="Z46" s="10"/>
+      <c r="AA46" s="10"/>
+      <c r="AB46" s="10"/>
+      <c r="AC46" s="10"/>
+      <c r="AD46" s="10"/>
+      <c r="AE46" s="10"/>
+      <c r="AF46" s="10"/>
+      <c r="AG46" s="10"/>
+      <c r="AH46" s="10"/>
+      <c r="AI46" s="10"/>
+      <c r="AJ46" s="10"/>
+      <c r="AK46" s="10"/>
+      <c r="AL46" s="10"/>
+    </row>
+    <row r="47" spans="1:38">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C47" s="10" t="b">
+      <c r="C47" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="D47" s="10" t="b">
+      <c r="E47" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="I47" s="10" t="s">
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="J47" s="10">
+      <c r="J47" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K47" s="9">
+        <v>0</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="M47" s="9"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="2"/>
+      <c r="W47" s="2"/>
+      <c r="X47" s="2"/>
+      <c r="Y47" s="2"/>
+      <c r="Z47" s="2"/>
+      <c r="AA47" s="2"/>
+      <c r="AB47" s="2"/>
+      <c r="AC47" s="2"/>
+      <c r="AD47" s="2"/>
+      <c r="AE47" s="2"/>
+      <c r="AF47" s="2"/>
+      <c r="AG47" s="2"/>
+      <c r="AH47" s="2"/>
+      <c r="AI47" s="2"/>
+      <c r="AJ47" s="2"/>
+      <c r="AK47" s="2"/>
+      <c r="AL47" s="2"/>
+    </row>
+    <row r="48" spans="1:38">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="K48" s="9">
         <v>1</v>
       </c>
-      <c r="K47" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="L47" s="10"/>
-    </row>
-    <row r="48" spans="2:12">
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="J48" s="10">
+      <c r="L48" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="M48" s="9"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
+      <c r="T48" s="2"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="2"/>
+      <c r="W48" s="2"/>
+      <c r="X48" s="2"/>
+      <c r="Y48" s="2"/>
+      <c r="Z48" s="2"/>
+      <c r="AA48" s="2"/>
+      <c r="AB48" s="2"/>
+      <c r="AC48" s="2"/>
+      <c r="AD48" s="2"/>
+      <c r="AE48" s="2"/>
+      <c r="AF48" s="2"/>
+      <c r="AG48" s="2"/>
+      <c r="AH48" s="2"/>
+      <c r="AI48" s="2"/>
+      <c r="AJ48" s="2"/>
+      <c r="AK48" s="2"/>
+      <c r="AL48" s="2"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D50" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K50" s="11">
+        <v>1</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="M50" s="11"/>
+    </row>
+    <row r="51" spans="3:13">
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="K51" s="11">
         <v>2</v>
       </c>
-      <c r="K48" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49" spans="2:12">
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="J49" s="10">
+      <c r="L51" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M51" s="11"/>
+    </row>
+    <row r="52" spans="3:13">
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K52" s="11">
         <v>3</v>
       </c>
-      <c r="K49" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="L49" s="10"/>
-    </row>
-    <row r="50" spans="2:12">
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C51" s="10" t="b">
+      <c r="L52" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="M52" s="11"/>
+    </row>
+    <row r="53" spans="3:13">
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D54" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="D51" s="10" t="b">
+      <c r="E54" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="J51" s="10">
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="K54" s="11">
         <v>1</v>
       </c>
-      <c r="K51" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="L51" s="10"/>
-    </row>
-    <row r="52" spans="2:12">
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="J52" s="10">
+      <c r="L54" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="M54" s="11"/>
+    </row>
+    <row r="55" spans="3:13">
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="K55" s="11">
         <v>2</v>
       </c>
-      <c r="K52" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="L52" s="10"/>
-    </row>
-    <row r="53" spans="2:12">
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="I53" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J53" s="10">
+      <c r="L55" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="M55" s="11"/>
+    </row>
+    <row r="56" spans="3:13">
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="K56" s="11">
         <v>3</v>
       </c>
-      <c r="K53" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="L53" s="10"/>
-    </row>
-    <row r="54" spans="2:12">
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="J54" s="10">
-        <v>4</v>
-      </c>
-      <c r="K54" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="L54" s="10"/>
-    </row>
-    <row r="55" spans="2:12">
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J55" s="10">
-        <v>5</v>
-      </c>
-      <c r="K55" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="L55" s="10"/>
-    </row>
-    <row r="56" spans="2:12">
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-    </row>
-    <row r="57" spans="1:12">
-      <c r="A57" t="s">
-        <v>133</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C57" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D57" s="11" t="b">
-        <v>1</v>
-      </c>
+      <c r="L56" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="M56" s="11"/>
+    </row>
+    <row r="57" spans="3:13">
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="11"/>
-      <c r="H57" s="11" t="s">
-        <v>45</v>
-      </c>
+      <c r="H57" s="11"/>
       <c r="I57" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J57" s="11">
-        <v>0</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="L57" s="11"/>
-    </row>
-    <row r="58" spans="2:12">
-      <c r="B58" s="11"/>
+        <v>34</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="K57" s="11">
+        <v>4</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="M57" s="11"/>
+    </row>
+    <row r="58" spans="3:13">
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
       <c r="G58" s="11"/>
-      <c r="H58" s="11" t="s">
-        <v>136</v>
-      </c>
+      <c r="H58" s="11"/>
       <c r="I58" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="J58" s="11">
+        <v>138</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="K58" s="11">
+        <v>5</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="M58" s="11"/>
+    </row>
+    <row r="59" spans="3:13">
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60"/>
+      <c r="B60" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D60" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="K58" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="L58" s="11"/>
-    </row>
-    <row r="59" spans="2:12">
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="I59" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="J59" s="11">
-        <v>2</v>
-      </c>
-      <c r="K59" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="L59" s="11"/>
-    </row>
-    <row r="60" spans="2:12">
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="I60" s="11" t="s">
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="J60" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K60" s="12">
+        <v>0</v>
+      </c>
+      <c r="L60" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="J60" s="11">
-        <v>3</v>
-      </c>
-      <c r="K60" s="11" t="s">
+      <c r="M60" s="12"/>
+    </row>
+    <row r="61" spans="3:13">
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="L60" s="11"/>
-    </row>
-    <row r="61" s="2" customFormat="1"/>
-    <row r="62" spans="1:12">
-      <c r="A62" s="2" t="s">
+      <c r="J61" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="K61" s="12">
+        <v>1</v>
+      </c>
+      <c r="L61" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="C62" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D62" s="12" t="b">
-        <v>1</v>
-      </c>
+      <c r="M61" s="12"/>
+    </row>
+    <row r="62" spans="3:13">
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
       <c r="E62" s="12"/>
       <c r="F62" s="12"/>
       <c r="G62" s="12"/>
-      <c r="H62" s="12" t="s">
+      <c r="H62" s="12"/>
+      <c r="I62" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="J62" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="J62" s="12">
-        <v>0</v>
-      </c>
-      <c r="K62" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="L62" s="12"/>
-    </row>
-    <row r="63" spans="1:12">
-      <c r="A63" s="2"/>
-      <c r="B63" s="12"/>
+      <c r="K62" s="12">
+        <v>2</v>
+      </c>
+      <c r="L62" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="M62" s="12"/>
+    </row>
+    <row r="63" spans="3:13">
       <c r="C63" s="12"/>
       <c r="D63" s="12"/>
       <c r="E63" s="12"/>
       <c r="F63" s="12"/>
       <c r="G63" s="12"/>
-      <c r="H63" s="12" t="s">
-        <v>149</v>
-      </c>
+      <c r="H63" s="12"/>
       <c r="I63" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="J63" s="12">
+      <c r="J63" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="K63" s="12">
+        <v>3</v>
+      </c>
+      <c r="L63" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="M63" s="12"/>
+    </row>
+    <row r="64" s="2" customFormat="1"/>
+    <row r="65" spans="1:13">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D65" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="J65" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="K65" s="16">
+        <v>0</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="M65" s="16"/>
+    </row>
+    <row r="66" spans="1:13">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="J66" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="K66" s="16">
         <v>1500</v>
       </c>
-      <c r="K63" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="L63" s="12"/>
-    </row>
-    <row r="64" spans="1:12">
-      <c r="A64" s="2"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="J64" s="12">
+      <c r="L66" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="M66" s="16"/>
+    </row>
+    <row r="67" spans="1:13">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="J67" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="K67" s="16">
         <v>2000</v>
       </c>
-      <c r="K64" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="L64" s="12"/>
-    </row>
-    <row r="65" spans="1:12">
-      <c r="A65" s="2"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="I65" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="J65" s="12">
+      <c r="L67" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="M67" s="16"/>
+    </row>
+    <row r="68" spans="1:13">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="16"/>
+      <c r="H68" s="16"/>
+      <c r="I68" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="J68" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="K68" s="16">
         <v>2500</v>
       </c>
-      <c r="K65" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="L65" s="12"/>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" s="2"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="J66" s="12">
+      <c r="L68" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="M68" s="16"/>
+    </row>
+    <row r="69" spans="1:13">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="J69" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="K69" s="16">
         <v>3000</v>
       </c>
-      <c r="K66" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="L66" s="12"/>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" s="2"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="I67" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J67" s="12">
+      <c r="L69" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="M69" s="16"/>
+    </row>
+    <row r="70" spans="1:13">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="J70" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="K70" s="16">
         <v>3500</v>
       </c>
-      <c r="K67" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="L67" s="12"/>
-    </row>
-    <row r="68" spans="1:12">
-      <c r="A68" s="2"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="J68" s="12">
+      <c r="L70" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="M70" s="16"/>
+    </row>
+    <row r="71" spans="1:13">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="J71" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="K71" s="16">
         <v>4000</v>
       </c>
-      <c r="K68" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="L68" s="12"/>
-    </row>
-    <row r="69" s="2" customFormat="1"/>
-    <row r="70" spans="1:12">
-      <c r="A70" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="C70" s="12" t="b">
+      <c r="L71" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M71" s="16"/>
+    </row>
+    <row r="72" s="2" customFormat="1"/>
+    <row r="73" spans="1:13">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D73" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="D70" s="12" t="b">
+      <c r="E73" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I70" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="J70" s="12">
+      <c r="F73" s="16"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J73" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="K73" s="16">
         <v>0</v>
       </c>
-      <c r="K70" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="L70" s="12"/>
-    </row>
-    <row r="71" spans="1:12">
-      <c r="A71" s="2"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="I71" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="J71" s="12">
+      <c r="L73" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="M73" s="16"/>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="J74" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="K74" s="16">
         <v>1</v>
       </c>
-      <c r="K71" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="L71" s="12"/>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" s="2"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="J72" s="12">
+      <c r="L74" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="M74" s="16"/>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="J75" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="K75" s="16">
         <v>2</v>
       </c>
-      <c r="K72" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="L72" s="12"/>
+      <c r="L75" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="M75" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="I1:M1"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Excels/__enums__.xlsx
+++ b/Config/Excels/__enums__.xlsx
@@ -14,14 +14,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>##注释</t>
-  </si>
-  <si>
     <t>full_name</t>
   </si>
   <si>
@@ -76,12 +73,12 @@
     <t>注释</t>
   </si>
   <si>
+    <t>EQuality</t>
+  </si>
+  <si>
     <t>品质</t>
   </si>
   <si>
-    <t>EQuality</t>
-  </si>
-  <si>
     <t>White</t>
   </si>
   <si>
@@ -112,12 +109,12 @@
     <t>橙</t>
   </si>
   <si>
+    <t>ItemType</t>
+  </si>
+  <si>
     <t>道具类型</t>
   </si>
   <si>
-    <t>ItemType</t>
-  </si>
-  <si>
     <t>Item</t>
   </si>
   <si>
@@ -148,12 +145,12 @@
     <t>材料</t>
   </si>
   <si>
+    <t>ItemSubType</t>
+  </si>
+  <si>
     <t>道具子类型</t>
   </si>
   <si>
-    <t>ItemSubType</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
@@ -190,12 +187,12 @@
     <t>戒指</t>
   </si>
   <si>
+    <t>ItemUseType</t>
+  </si>
+  <si>
     <t>道具使用类型</t>
   </si>
   <si>
-    <t>ItemUseType</t>
-  </si>
-  <si>
     <t>CanNot</t>
   </si>
   <si>
@@ -217,12 +214,12 @@
     <t>可一键全部使用</t>
   </si>
   <si>
+    <t>ERedDotKey</t>
+  </si>
+  <si>
     <t>红点枚举类型</t>
   </si>
   <si>
-    <t>ERedDotKey</t>
-  </si>
-  <si>
     <t>Bag</t>
   </si>
   <si>
@@ -295,12 +292,12 @@
     <t>战斗.队伍</t>
   </si>
   <si>
+    <t>ERedDotDisplayMode</t>
+  </si>
+  <si>
     <t>红点显示类型</t>
   </si>
   <si>
-    <t>ERedDotDisplayMode</t>
-  </si>
-  <si>
     <t>DotOnly</t>
   </si>
   <si>
@@ -319,12 +316,12 @@
     <t>自动</t>
   </si>
   <si>
+    <t>ERedDotCleanStrategy</t>
+  </si>
+  <si>
     <t>红点清除策略类型</t>
   </si>
   <si>
-    <t>ERedDotCleanStrategy</t>
-  </si>
-  <si>
     <t>Manual</t>
   </si>
   <si>
@@ -343,12 +340,12 @@
     <t>界面关闭时框架自动清除</t>
   </si>
   <si>
+    <t>ERedDotLogicType</t>
+  </si>
+  <si>
     <t>红点计算逻辑类型</t>
   </si>
   <si>
-    <t>ERedDotLogicType</t>
-  </si>
-  <si>
     <t>Sum</t>
   </si>
   <si>
@@ -364,12 +361,12 @@
     <t>任意一个即可</t>
   </si>
   <si>
+    <t>ESoundGroup</t>
+  </si>
+  <si>
     <t>声音组</t>
   </si>
   <si>
-    <t>ESoundGroup</t>
-  </si>
-  <si>
     <t>BGM</t>
   </si>
   <si>
@@ -397,12 +394,12 @@
     <t>UI音效</t>
   </si>
   <si>
+    <t>EEntityGroup</t>
+  </si>
+  <si>
     <t>实体组</t>
   </si>
   <si>
-    <t>EEntityGroup</t>
-  </si>
-  <si>
     <t>Player</t>
   </si>
   <si>
@@ -439,12 +436,12 @@
     <t>特效</t>
   </si>
   <si>
+    <t>EStepType</t>
+  </si>
+  <si>
     <t>引导步骤类型</t>
   </si>
   <si>
-    <t>EStepType</t>
-  </si>
-  <si>
     <t>无类型</t>
   </si>
   <si>
@@ -475,12 +472,12 @@
     <t>等待步骤</t>
   </si>
   <si>
+    <t>EUILayer</t>
+  </si>
+  <si>
     <t>UI界面层级</t>
   </si>
   <si>
-    <t>EUILayer</t>
-  </si>
-  <si>
     <t>WorldUI</t>
   </si>
   <si>
@@ -523,10 +520,10 @@
     <t>加载界面</t>
   </si>
   <si>
+    <t>EUITweenType</t>
+  </si>
+  <si>
     <t>UI界面动画类型</t>
-  </si>
-  <si>
-    <t>EUITweenType</t>
   </si>
   <si>
     <t>无动画</t>
@@ -549,10 +546,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -570,8 +567,129 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -586,133 +704,12 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="40">
     <fill>
@@ -771,13 +768,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -789,7 +810,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -801,151 +942,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -999,21 +996,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1032,7 +1014,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1041,7 +1023,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1057,6 +1054,17 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1084,17 +1092,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1103,10 +1100,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="4">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
@@ -1115,133 +1112,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1265,26 +1262,26 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="31" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="31" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1610,23 +1607,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AL75"/>
+  <dimension ref="A1:AK75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="17.125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22.375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="14.125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="7.125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="5" style="5" customWidth="1"/>
-    <col min="9" max="9" width="13" style="5" customWidth="1"/>
-    <col min="10" max="10" width="16.5" style="5" customWidth="1"/>
-    <col min="11" max="11" width="12.125" style="5" customWidth="1"/>
-    <col min="12" max="12" width="26.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="17.125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22.375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="5" customWidth="1"/>
+    <col min="7" max="7" width="5" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13" style="5" customWidth="1"/>
+    <col min="9" max="9" width="16.5" style="5" customWidth="1"/>
+    <col min="10" max="10" width="12.125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="26.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="29" customHeight="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" ht="29" customHeight="1" spans="1:12">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1648,18 +1645,15 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
-        <v>8</v>
-      </c>
+      <c r="I1" s="14"/>
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="15"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:13">
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:12">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -1669,7 +1663,9 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="H2" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
@@ -1677,32 +1673,31 @@
         <v>10</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:13">
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:12">
       <c r="A3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
+      <c r="H3" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I3" s="6" t="s">
         <v>16</v>
       </c>
@@ -1712,126 +1707,122 @@
       <c r="K3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="2:12">
+      <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="2:13">
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="G4" s="8"/>
+      <c r="H4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="b">
+      <c r="I4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="8">
         <v>1</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="2:12">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="7">
-        <v>1</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" s="7"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="3:13">
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="8">
+        <v>2</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="2:12">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="7">
-        <v>2</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="7"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="3:13">
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="8">
+        <v>3</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="2:12">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="7">
-        <v>3</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="7"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="3:13">
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="8">
+        <v>4</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="2:12">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="7">
-        <v>4</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="3:13">
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="7">
+      <c r="J8" s="8">
         <v>5</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" spans="1:38">
+      <c r="K8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" spans="1:37">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1869,123 +1860,121 @@
       <c r="AI9" s="2"/>
       <c r="AJ9" s="2"/>
       <c r="AK9" s="2"/>
-      <c r="AL9" s="2"/>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="2:13">
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="10" s="2" customFormat="1" spans="2:12">
+      <c r="B10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="G10" s="9"/>
+      <c r="H10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8" t="b">
+      <c r="I10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="9">
         <v>1</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8" t="s">
+      <c r="K10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="L10" s="9"/>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="2:12">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K10" s="8">
-        <v>1</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M10" s="8"/>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="3:13">
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="9">
+        <v>2</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="2:12">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K11" s="8">
-        <v>2</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="M11" s="8"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="3:13">
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="9">
+        <v>3</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" s="9"/>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="2:12">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K12" s="8">
-        <v>3</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" s="8"/>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="3:13">
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="9">
+        <v>4</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="2:12">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="8">
-        <v>4</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M13" s="8"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="3:13">
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" s="8">
+      <c r="J14" s="9">
         <v>5</v>
       </c>
-      <c r="L14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="M14" s="8"/>
-    </row>
-    <row r="15" spans="1:38">
+      <c r="K14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="1:37">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2023,144 +2012,142 @@
       <c r="AI15" s="2"/>
       <c r="AJ15" s="2"/>
       <c r="AK15" s="2"/>
-      <c r="AL15" s="2"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="2:13">
-      <c r="B16" s="2" t="s">
+    </row>
+    <row r="16" s="2" customFormat="1" spans="2:12">
+      <c r="B16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="G16" s="9"/>
+      <c r="H16" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="8" t="b">
+      <c r="I16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="9">
         <v>0</v>
       </c>
-      <c r="E16" s="8" t="b">
+      <c r="K16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="2:12">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" s="9">
         <v>1</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="K16" s="8">
-        <v>0</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M16" s="8"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="3:13">
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
+      <c r="K17" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="2:12">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K17" s="8">
-        <v>1</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="M17" s="8"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="3:13">
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="9">
+        <v>2</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="2:12">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="K18" s="8">
-        <v>2</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="M18" s="8"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="3:13">
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="9">
+        <v>3</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="9"/>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="2:12">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="K19" s="8">
-        <v>3</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="M19" s="8"/>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="3:13">
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="9">
+        <v>4</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L20" s="9"/>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="2:12">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K20" s="8">
-        <v>4</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M20" s="8"/>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="3:13">
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="J21" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K21" s="8">
+      <c r="J21" s="9">
         <v>5</v>
       </c>
-      <c r="L21" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M21" s="8"/>
-    </row>
-    <row r="22" spans="1:38">
+      <c r="K21" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" spans="1:37">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2198,81 +2185,79 @@
       <c r="AI22" s="2"/>
       <c r="AJ22" s="2"/>
       <c r="AK22" s="2"/>
-      <c r="AL22" s="2"/>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="2:13">
-      <c r="B23" s="2" t="s">
+    </row>
+    <row r="23" s="2" customFormat="1" spans="2:12">
+      <c r="B23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="G23" s="9"/>
+      <c r="H23" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="8" t="b">
+      <c r="I23" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J23" s="9">
         <v>0</v>
       </c>
-      <c r="E23" s="8" t="b">
+      <c r="K23" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="L23" s="9"/>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="2:12">
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J24" s="9">
         <v>1</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K23" s="8">
-        <v>0</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M23" s="8"/>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="3:13">
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8" t="s">
+      <c r="K24" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="L24" s="9"/>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="2:12">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="K24" s="8">
-        <v>1</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="M24" s="8"/>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="3:13">
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="9">
+        <v>2</v>
+      </c>
+      <c r="K25" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K25" s="8">
-        <v>2</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="M25" s="8"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:38">
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="1:37">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2310,38 +2295,37 @@
       <c r="AI26" s="2"/>
       <c r="AJ26" s="2"/>
       <c r="AK26" s="2"/>
-      <c r="AL26" s="2"/>
-    </row>
-    <row r="27" spans="1:38">
+    </row>
+    <row r="27" spans="1:37">
       <c r="A27" s="2"/>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="G27" s="10"/>
+      <c r="H27" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J27" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="K27" s="9">
+      <c r="J27" s="10">
         <v>1000</v>
       </c>
-      <c r="L27" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="M27" s="9"/>
+      <c r="K27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L27" s="10"/>
+      <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -2366,30 +2350,29 @@
       <c r="AI27" s="2"/>
       <c r="AJ27" s="2"/>
       <c r="AK27" s="2"/>
-      <c r="AL27" s="2"/>
-    </row>
-    <row r="28" spans="1:38">
+    </row>
+    <row r="28" spans="1:37">
       <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9" t="s">
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="J28" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="K28" s="9">
+      <c r="J28" s="10">
         <v>1001</v>
       </c>
-      <c r="L28" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="M28" s="9"/>
+      <c r="K28" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="L28" s="10"/>
+      <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -2414,30 +2397,29 @@
       <c r="AI28" s="2"/>
       <c r="AJ28" s="2"/>
       <c r="AK28" s="2"/>
-      <c r="AL28" s="2"/>
-    </row>
-    <row r="29" spans="1:38">
+    </row>
+    <row r="29" spans="1:37">
       <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9" t="s">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J29" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="K29" s="9">
+      <c r="J29" s="10">
         <v>1002</v>
       </c>
-      <c r="L29" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="M29" s="9"/>
+      <c r="K29" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="L29" s="10"/>
+      <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -2462,30 +2444,29 @@
       <c r="AI29" s="2"/>
       <c r="AJ29" s="2"/>
       <c r="AK29" s="2"/>
-      <c r="AL29" s="2"/>
-    </row>
-    <row r="30" spans="1:38">
+    </row>
+    <row r="30" spans="1:37">
       <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9" t="s">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="J30" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="K30" s="9">
+      <c r="J30" s="10">
         <v>2000</v>
       </c>
-      <c r="L30" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="M30" s="9"/>
+      <c r="K30" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="L30" s="10"/>
+      <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -2510,30 +2491,29 @@
       <c r="AI30" s="2"/>
       <c r="AJ30" s="2"/>
       <c r="AK30" s="2"/>
-      <c r="AL30" s="2"/>
-    </row>
-    <row r="31" spans="1:38">
+    </row>
+    <row r="31" spans="1:37">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9" t="s">
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I31" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="J31" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="K31" s="9">
+      <c r="J31" s="10">
         <v>2001</v>
       </c>
-      <c r="L31" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="M31" s="9"/>
+      <c r="K31" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="L31" s="10"/>
+      <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -2558,30 +2538,29 @@
       <c r="AI31" s="2"/>
       <c r="AJ31" s="2"/>
       <c r="AK31" s="2"/>
-      <c r="AL31" s="2"/>
-    </row>
-    <row r="32" spans="1:38">
+    </row>
+    <row r="32" spans="1:37">
       <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9" t="s">
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I32" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="J32" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="K32" s="9">
+      <c r="J32" s="10">
         <v>2002</v>
       </c>
-      <c r="L32" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="M32" s="9"/>
+      <c r="K32" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L32" s="10"/>
+      <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -2606,30 +2585,29 @@
       <c r="AI32" s="2"/>
       <c r="AJ32" s="2"/>
       <c r="AK32" s="2"/>
-      <c r="AL32" s="2"/>
-    </row>
-    <row r="33" spans="1:38">
+    </row>
+    <row r="33" spans="1:37">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9" t="s">
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I33" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="J33" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="K33" s="9">
+      <c r="J33" s="10">
         <v>3000</v>
       </c>
-      <c r="L33" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="M33" s="9"/>
+      <c r="K33" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="L33" s="10"/>
+      <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -2654,30 +2632,29 @@
       <c r="AI33" s="2"/>
       <c r="AJ33" s="2"/>
       <c r="AK33" s="2"/>
-      <c r="AL33" s="2"/>
-    </row>
-    <row r="34" spans="1:38">
+    </row>
+    <row r="34" spans="1:37">
       <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9" t="s">
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I34" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="J34" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="K34" s="9">
+      <c r="J34" s="10">
         <v>3001</v>
       </c>
-      <c r="L34" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="M34" s="9"/>
+      <c r="K34" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="L34" s="10"/>
+      <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -2702,30 +2679,29 @@
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
       <c r="AK34" s="2"/>
-      <c r="AL34" s="2"/>
-    </row>
-    <row r="35" spans="1:38">
+    </row>
+    <row r="35" spans="1:37">
       <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9" t="s">
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I35" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="J35" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="K35" s="9">
+      <c r="J35" s="10">
         <v>3002</v>
       </c>
-      <c r="L35" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="M35" s="9"/>
+      <c r="K35" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="L35" s="10"/>
+      <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -2750,30 +2726,29 @@
       <c r="AI35" s="2"/>
       <c r="AJ35" s="2"/>
       <c r="AK35" s="2"/>
-      <c r="AL35" s="2"/>
-    </row>
-    <row r="36" spans="1:38">
+    </row>
+    <row r="36" spans="1:37">
       <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9" t="s">
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I36" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J36" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K36" s="9">
+      <c r="J36" s="10">
         <v>3003</v>
       </c>
-      <c r="L36" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M36" s="9"/>
+      <c r="K36" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="L36" s="10"/>
+      <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -2798,30 +2773,29 @@
       <c r="AI36" s="2"/>
       <c r="AJ36" s="2"/>
       <c r="AK36" s="2"/>
-      <c r="AL36" s="2"/>
-    </row>
-    <row r="37" spans="1:38">
+    </row>
+    <row r="37" spans="1:37">
       <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9" t="s">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I37" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="J37" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="K37" s="9">
+      <c r="J37" s="10">
         <v>4000</v>
       </c>
-      <c r="L37" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="M37" s="9"/>
+      <c r="K37" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L37" s="10"/>
+      <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -2846,30 +2820,29 @@
       <c r="AI37" s="2"/>
       <c r="AJ37" s="2"/>
       <c r="AK37" s="2"/>
-      <c r="AL37" s="2"/>
-    </row>
-    <row r="38" spans="1:38">
+    </row>
+    <row r="38" spans="1:37">
       <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I38" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="J38" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="K38" s="9">
+      <c r="J38" s="10">
         <v>4001</v>
       </c>
-      <c r="L38" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="M38" s="9"/>
+      <c r="K38" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="L38" s="10"/>
+      <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -2894,9 +2867,8 @@
       <c r="AI38" s="2"/>
       <c r="AJ38" s="2"/>
       <c r="AK38" s="2"/>
-      <c r="AL38" s="2"/>
-    </row>
-    <row r="39" spans="1:38">
+    </row>
+    <row r="39" spans="1:37">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2934,38 +2906,37 @@
       <c r="AI39" s="2"/>
       <c r="AJ39" s="2"/>
       <c r="AK39" s="2"/>
-      <c r="AL39" s="2"/>
-    </row>
-    <row r="40" spans="1:38">
+    </row>
+    <row r="40" spans="1:37">
       <c r="A40" s="2"/>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="G40" s="10"/>
+      <c r="H40" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D40" s="9" t="b">
+      <c r="I40" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="J40" s="10">
         <v>0</v>
       </c>
-      <c r="E40" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9" t="s">
+      <c r="K40" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="J40" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="K40" s="9">
-        <v>0</v>
-      </c>
-      <c r="L40" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="M40" s="9"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -2990,30 +2961,29 @@
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
       <c r="AK40" s="2"/>
-      <c r="AL40" s="2"/>
-    </row>
-    <row r="41" spans="1:38">
+    </row>
+    <row r="41" spans="1:37">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9" t="s">
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I41" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="J41" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="K41" s="9">
+      <c r="J41" s="10">
         <v>1</v>
       </c>
-      <c r="L41" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="M41" s="9"/>
+      <c r="K41" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L41" s="10"/>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
@@ -3038,28 +3008,27 @@
       <c r="AI41" s="2"/>
       <c r="AJ41" s="2"/>
       <c r="AK41" s="2"/>
-      <c r="AL41" s="2"/>
-    </row>
-    <row r="42" spans="1:38">
+    </row>
+    <row r="42" spans="1:37">
       <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9" t="s">
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I42" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="J42" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K42" s="9">
+      <c r="J42" s="10">
         <v>2</v>
       </c>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -3084,9 +3053,8 @@
       <c r="AI42" s="2"/>
       <c r="AJ42" s="2"/>
       <c r="AK42" s="2"/>
-      <c r="AL42" s="2"/>
-    </row>
-    <row r="43" spans="1:38">
+    </row>
+    <row r="43" spans="1:37">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3124,38 +3092,37 @@
       <c r="AI43" s="2"/>
       <c r="AJ43" s="2"/>
       <c r="AK43" s="2"/>
-      <c r="AL43" s="2"/>
-    </row>
-    <row r="44" spans="1:38">
+    </row>
+    <row r="44" spans="1:37">
       <c r="A44" s="2"/>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="G44" s="10"/>
+      <c r="H44" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D44" s="9" t="b">
+      <c r="I44" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="J44" s="10">
         <v>0</v>
       </c>
-      <c r="E44" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="J44" s="9" t="s">
+      <c r="K44" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="K44" s="9">
-        <v>0</v>
-      </c>
-      <c r="L44" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="M44" s="9"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
@@ -3180,30 +3147,29 @@
       <c r="AI44" s="2"/>
       <c r="AJ44" s="2"/>
       <c r="AK44" s="2"/>
-      <c r="AL44" s="2"/>
-    </row>
-    <row r="45" spans="1:38">
+    </row>
+    <row r="45" spans="1:37">
       <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9" t="s">
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="I45" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="J45" s="9" t="s">
+      <c r="J45" s="10">
+        <v>1</v>
+      </c>
+      <c r="K45" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K45" s="9">
-        <v>1</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="M45" s="9"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
@@ -3228,78 +3194,76 @@
       <c r="AI45" s="2"/>
       <c r="AJ45" s="2"/>
       <c r="AK45" s="2"/>
-      <c r="AL45" s="2"/>
-    </row>
-    <row r="46" s="4" customFormat="1" spans="1:38">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="10"/>
-      <c r="S46" s="10"/>
-      <c r="T46" s="10"/>
-      <c r="U46" s="10"/>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10"/>
-      <c r="X46" s="10"/>
-      <c r="Y46" s="10"/>
-      <c r="Z46" s="10"/>
-      <c r="AA46" s="10"/>
-      <c r="AB46" s="10"/>
-      <c r="AC46" s="10"/>
-      <c r="AD46" s="10"/>
-      <c r="AE46" s="10"/>
-      <c r="AF46" s="10"/>
-      <c r="AG46" s="10"/>
-      <c r="AH46" s="10"/>
-      <c r="AI46" s="10"/>
-      <c r="AJ46" s="10"/>
-      <c r="AK46" s="10"/>
-      <c r="AL46" s="10"/>
-    </row>
-    <row r="47" spans="1:38">
+    </row>
+    <row r="46" s="4" customFormat="1" spans="1:37">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
+      <c r="T46" s="11"/>
+      <c r="U46" s="11"/>
+      <c r="V46" s="11"/>
+      <c r="W46" s="11"/>
+      <c r="X46" s="11"/>
+      <c r="Y46" s="11"/>
+      <c r="Z46" s="11"/>
+      <c r="AA46" s="11"/>
+      <c r="AB46" s="11"/>
+      <c r="AC46" s="11"/>
+      <c r="AD46" s="11"/>
+      <c r="AE46" s="11"/>
+      <c r="AF46" s="11"/>
+      <c r="AG46" s="11"/>
+      <c r="AH46" s="11"/>
+      <c r="AI46" s="11"/>
+      <c r="AJ46" s="11"/>
+      <c r="AK46" s="11"/>
+    </row>
+    <row r="47" spans="1:37">
       <c r="A47" s="2"/>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="G47" s="10"/>
+      <c r="H47" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="9" t="b">
+      <c r="I47" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J47" s="10">
         <v>0</v>
       </c>
-      <c r="E47" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="J47" s="9" t="s">
+      <c r="K47" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="K47" s="9">
-        <v>0</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="M47" s="9"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -3324,30 +3288,29 @@
       <c r="AI47" s="2"/>
       <c r="AJ47" s="2"/>
       <c r="AK47" s="2"/>
-      <c r="AL47" s="2"/>
-    </row>
-    <row r="48" spans="1:38">
+    </row>
+    <row r="48" spans="1:37">
       <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="9" t="s">
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I48" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="J48" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="K48" s="9">
+      <c r="J48" s="10">
         <v>1</v>
       </c>
-      <c r="L48" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="M48" s="9"/>
+      <c r="K48" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="L48" s="10"/>
+      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
@@ -3372,82 +3335,81 @@
       <c r="AI48" s="2"/>
       <c r="AJ48" s="2"/>
       <c r="AK48" s="2"/>
-      <c r="AL48" s="2"/>
-    </row>
-    <row r="50" spans="1:13">
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" s="2"/>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="G50" s="12"/>
+      <c r="H50" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D50" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" s="11" t="b">
+      <c r="I50" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="J50" s="12">
         <v>1</v>
       </c>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="J50" s="11" t="s">
+      <c r="K50" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="K50" s="11">
-        <v>1</v>
-      </c>
-      <c r="L50" s="11" t="s">
+      <c r="L50" s="12"/>
+    </row>
+    <row r="51" spans="2:12">
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="M50" s="11"/>
-    </row>
-    <row r="51" spans="3:13">
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J51" s="12">
+        <v>2</v>
+      </c>
+      <c r="K51" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="K51" s="11">
-        <v>2</v>
-      </c>
-      <c r="L51" s="11" t="s">
+      <c r="L51" s="12"/>
+    </row>
+    <row r="52" spans="2:12">
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="M51" s="11"/>
-    </row>
-    <row r="52" spans="3:13">
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="12">
+        <v>3</v>
+      </c>
+      <c r="K52" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="K52" s="11">
-        <v>3</v>
-      </c>
-      <c r="L52" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="M52" s="11"/>
-    </row>
-    <row r="53" spans="3:13">
+      <c r="L52" s="12"/>
+    </row>
+    <row r="53" spans="2:12">
+      <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -3458,124 +3420,123 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-    </row>
-    <row r="54" spans="1:13">
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" s="2"/>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="G54" s="12"/>
+      <c r="H54" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="D54" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="E54" s="11" t="b">
+      <c r="I54" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="J54" s="12">
         <v>1</v>
       </c>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="J54" s="11" t="s">
+      <c r="K54" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="K54" s="11">
-        <v>1</v>
-      </c>
-      <c r="L54" s="11" t="s">
+      <c r="L54" s="12"/>
+    </row>
+    <row r="55" spans="2:12">
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="M54" s="11"/>
-    </row>
-    <row r="55" spans="3:13">
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="J55" s="11" t="s">
+      <c r="J55" s="12">
+        <v>2</v>
+      </c>
+      <c r="K55" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="K55" s="11">
-        <v>2</v>
-      </c>
-      <c r="L55" s="11" t="s">
+      <c r="L55" s="12"/>
+    </row>
+    <row r="56" spans="2:12">
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="M55" s="11"/>
-    </row>
-    <row r="56" spans="3:13">
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="J56" s="12">
+        <v>3</v>
+      </c>
+      <c r="K56" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="L56" s="12"/>
+    </row>
+    <row r="57" spans="2:12">
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I57" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="K56" s="11">
-        <v>3</v>
-      </c>
-      <c r="L56" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="M56" s="11"/>
-    </row>
-    <row r="57" spans="3:13">
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11" t="s">
+      <c r="J57" s="12">
+        <v>4</v>
+      </c>
+      <c r="K57" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="L57" s="12"/>
+    </row>
+    <row r="58" spans="2:12">
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="K57" s="11">
-        <v>4</v>
-      </c>
-      <c r="L57" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M57" s="11"/>
-    </row>
-    <row r="58" spans="3:13">
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="12">
+        <v>5</v>
+      </c>
+      <c r="K58" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="K58" s="11">
-        <v>5</v>
-      </c>
-      <c r="L58" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="M58" s="11"/>
-    </row>
-    <row r="59" spans="3:13">
+      <c r="L58" s="12"/>
+    </row>
+    <row r="59" spans="2:12">
+      <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
@@ -3586,353 +3547,341 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-    </row>
-    <row r="60" spans="1:13">
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60"/>
-      <c r="B60" t="s">
+      <c r="B60" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C60" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="G60" s="13"/>
+      <c r="H60" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I60" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J60" s="13">
+        <v>0</v>
+      </c>
+      <c r="K60" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D60" s="12" t="b">
+      <c r="L60" s="13"/>
+    </row>
+    <row r="61" spans="2:12">
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="I61" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="J61" s="13">
+        <v>1</v>
+      </c>
+      <c r="K61" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="L61" s="13"/>
+    </row>
+    <row r="62" spans="2:12">
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="I62" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="J62" s="13">
+        <v>2</v>
+      </c>
+      <c r="K62" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="L62" s="13"/>
+    </row>
+    <row r="63" spans="2:12">
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="I63" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="J63" s="13">
+        <v>3</v>
+      </c>
+      <c r="K63" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="L63" s="13"/>
+    </row>
+    <row r="64" s="2" customFormat="1"/>
+    <row r="65" spans="1:12">
+      <c r="A65" s="2"/>
+      <c r="B65" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E60" s="12" t="b">
+      <c r="D65" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="J60" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="K60" s="12">
-        <v>0</v>
-      </c>
-      <c r="L60" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="M60" s="12"/>
-    </row>
-    <row r="61" spans="3:13">
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="J61" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="K61" s="12">
-        <v>1</v>
-      </c>
-      <c r="L61" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="M61" s="12"/>
-    </row>
-    <row r="62" spans="3:13">
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="J62" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="K62" s="12">
-        <v>2</v>
-      </c>
-      <c r="L62" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="M62" s="12"/>
-    </row>
-    <row r="63" spans="3:13">
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="K63" s="12">
-        <v>3</v>
-      </c>
-      <c r="L63" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="M63" s="12"/>
-    </row>
-    <row r="64" s="2" customFormat="1"/>
-    <row r="65" spans="1:13">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2" t="s">
+      <c r="E65" s="16"/>
+      <c r="F65" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="G65" s="16"/>
+      <c r="H65" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="D65" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E65" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
-      <c r="H65" s="16"/>
       <c r="I65" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="J65" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="K65" s="16">
+      <c r="J65" s="16">
         <v>0</v>
       </c>
-      <c r="L65" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="M65" s="16"/>
-    </row>
-    <row r="66" spans="1:13">
+      <c r="K65" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="L65" s="16"/>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
+      <c r="B66" s="16"/>
       <c r="C66" s="16"/>
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
       <c r="F66" s="16"/>
       <c r="G66" s="16"/>
-      <c r="H66" s="16"/>
+      <c r="H66" s="16" t="s">
+        <v>156</v>
+      </c>
       <c r="I66" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="J66" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="K66" s="16">
+      <c r="J66" s="16">
         <v>1500</v>
       </c>
-      <c r="L66" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="M66" s="16"/>
-    </row>
-    <row r="67" spans="1:13">
+      <c r="K66" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="L66" s="16"/>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
+      <c r="B67" s="16"/>
       <c r="C67" s="16"/>
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
       <c r="F67" s="16"/>
       <c r="G67" s="16"/>
-      <c r="H67" s="16"/>
+      <c r="H67" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="I67" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="J67" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="K67" s="16">
+      <c r="J67" s="16">
         <v>2000</v>
       </c>
-      <c r="L67" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="M67" s="16"/>
-    </row>
-    <row r="68" spans="1:13">
+      <c r="K67" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="L67" s="16"/>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="16"/>
       <c r="C68" s="16"/>
       <c r="D68" s="16"/>
       <c r="E68" s="16"/>
       <c r="F68" s="16"/>
       <c r="G68" s="16"/>
-      <c r="H68" s="16"/>
+      <c r="H68" s="16" t="s">
+        <v>160</v>
+      </c>
       <c r="I68" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="J68" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="K68" s="16">
+      <c r="J68" s="16">
         <v>2500</v>
       </c>
-      <c r="L68" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="M68" s="16"/>
-    </row>
-    <row r="69" spans="1:13">
+      <c r="K68" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="L68" s="16"/>
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
+      <c r="B69" s="16"/>
       <c r="C69" s="16"/>
       <c r="D69" s="16"/>
       <c r="E69" s="16"/>
       <c r="F69" s="16"/>
       <c r="G69" s="16"/>
-      <c r="H69" s="16"/>
+      <c r="H69" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="I69" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="J69" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="K69" s="16">
+      <c r="J69" s="16">
         <v>3000</v>
       </c>
-      <c r="L69" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="M69" s="16"/>
-    </row>
-    <row r="70" spans="1:13">
+      <c r="K69" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="L69" s="16"/>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
+      <c r="B70" s="16"/>
       <c r="C70" s="16"/>
       <c r="D70" s="16"/>
       <c r="E70" s="16"/>
       <c r="F70" s="16"/>
       <c r="G70" s="16"/>
-      <c r="H70" s="16"/>
+      <c r="H70" s="16" t="s">
+        <v>164</v>
+      </c>
       <c r="I70" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="J70" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="K70" s="16">
+      <c r="J70" s="16">
         <v>3500</v>
       </c>
-      <c r="L70" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="M70" s="16"/>
-    </row>
-    <row r="71" spans="1:13">
+      <c r="K70" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="L70" s="16"/>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
+      <c r="B71" s="16"/>
       <c r="C71" s="16"/>
       <c r="D71" s="16"/>
       <c r="E71" s="16"/>
       <c r="F71" s="16"/>
       <c r="G71" s="16"/>
-      <c r="H71" s="16"/>
+      <c r="H71" s="16" t="s">
+        <v>166</v>
+      </c>
       <c r="I71" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="J71" s="16" t="s">
+      <c r="J71" s="16">
+        <v>4000</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="L71" s="16"/>
+    </row>
+    <row r="72" s="2" customFormat="1"/>
+    <row r="73" spans="1:12">
+      <c r="A73" s="2"/>
+      <c r="B73" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="K71" s="16">
-        <v>4000</v>
-      </c>
-      <c r="L71" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="M71" s="16"/>
-    </row>
-    <row r="72" s="2" customFormat="1"/>
-    <row r="73" spans="1:13">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D73" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="C73" s="16" t="s">
+      <c r="G73" s="16"/>
+      <c r="H73" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I73" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="D73" s="16" t="b">
+      <c r="J73" s="16">
         <v>0</v>
       </c>
-      <c r="E73" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
-      <c r="H73" s="16"/>
-      <c r="I73" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="J73" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="K73" s="16">
-        <v>0</v>
-      </c>
-      <c r="L73" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="M73" s="16"/>
-    </row>
-    <row r="74" spans="1:13">
+      <c r="K73" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="L73" s="16"/>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
+      <c r="B74" s="16"/>
       <c r="C74" s="16"/>
       <c r="D74" s="16"/>
       <c r="E74" s="16"/>
       <c r="F74" s="16"/>
       <c r="G74" s="16"/>
-      <c r="H74" s="16"/>
+      <c r="H74" s="16" t="s">
+        <v>171</v>
+      </c>
       <c r="I74" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="J74" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="K74" s="16">
+      <c r="J74" s="16">
         <v>1</v>
       </c>
-      <c r="L74" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="M74" s="16"/>
-    </row>
-    <row r="75" spans="1:13">
+      <c r="K74" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="L74" s="16"/>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
+      <c r="B75" s="16"/>
       <c r="C75" s="16"/>
       <c r="D75" s="16"/>
       <c r="E75" s="16"/>
       <c r="F75" s="16"/>
       <c r="G75" s="16"/>
-      <c r="H75" s="16"/>
+      <c r="H75" s="16" t="s">
+        <v>173</v>
+      </c>
       <c r="I75" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="J75" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="K75" s="16">
+      <c r="J75" s="16">
         <v>2</v>
       </c>
-      <c r="L75" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="M75" s="16"/>
+      <c r="K75" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="L75" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
